--- a/docs/Cadrage projet/product-backlog.xlsx
+++ b/docs/Cadrage projet/product-backlog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nastry Gamer\Desktop\Programation\Cours\IPSSI_APOCAL_KIT\docs\Cadrage projet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38262173-E79B-409E-BC31-3FC087A70ABB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F33E4BF5-E345-4AC4-A702-9E4144E0BE9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garde" sheetId="1" r:id="rId1"/>
@@ -37,30 +37,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="193">
   <si>
     <t>A</t>
   </si>
@@ -95,31 +73,16 @@
     <t>Membres</t>
   </si>
   <si>
-    <t>[ Prénoms NOMS, séparés par virgule ]</t>
-  </si>
-  <si>
     <t>Sprint concerné</t>
   </si>
   <si>
-    <t>[ Cadrage / Sprint 1 / ... / Sprint 7 ]</t>
-  </si>
-  <si>
     <t>Version</t>
   </si>
   <si>
-    <t>[ v1.0 · v1.1 · v2.0 ]</t>
-  </si>
-  <si>
     <t>Date de remise</t>
   </si>
   <si>
-    <t>[ JJ/MM/AAAA  HHhMM ]</t>
-  </si>
-  <si>
     <t>Statut</t>
-  </si>
-  <si>
-    <t>[ Draft · En revue PO · Validé PO · Archivé ]</t>
   </si>
   <si>
     <t>💡 Convention de nommage du fichier :</t>
@@ -651,6 +614,21 @@
   </si>
   <si>
     <t>Toutes les stories ont été passées au crible INVEST en équipe</t>
+  </si>
+  <si>
+    <t>Tristan DZIOCH · Sebastien GERARD · Syphax ALILI · Killian MARTINS · Amine TALEB · Jacqueline MAPENZI · Moussa DIOP</t>
+  </si>
+  <si>
+    <t>v1.0</t>
+  </si>
+  <si>
+    <t>Draft</t>
+  </si>
+  <si>
+    <t>Cadrage</t>
+  </si>
+  <si>
+    <t>29/06/2026 17h45</t>
   </si>
 </sst>
 </file>
@@ -1313,7 +1291,7 @@
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="3" max="3" width="105" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:3" ht="15.75" x14ac:dyDescent="0.25">
@@ -1339,49 +1317,49 @@
         <v>10</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>11</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>13</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="10" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>15</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>17</v>
+        <v>192</v>
       </c>
     </row>
     <row r="10" spans="2:3" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>19</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B12" s="12" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1391,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1404,144 +1382,153 @@
   <sheetData>
     <row r="1" spans="1:10" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D6" s="14" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="E6" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="e" cm="1">
-        <f t="array" ref="J6">SUMPRODUCT((Backlog!A$2:A$21=D7)*(Backlog!J$2:J$21&lt;&gt;"Won't")*Backlog!F$2:F$21)</f>
-        <v>#VALUE!</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E7" s="16">
         <v>24</v>
       </c>
+      <c r="J7" s="31"/>
     </row>
     <row r="8" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B8" s="16" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="E8" s="16">
         <v>18</v>
       </c>
+      <c r="J8" s="31"/>
     </row>
     <row r="9" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B9" s="16" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>35</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="E9" s="16">
+        <v>47</v>
+      </c>
+      <c r="J9" s="31"/>
     </row>
     <row r="10" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>35</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="E10" s="16">
+        <v>22</v>
+      </c>
+      <c r="J10" s="31"/>
     </row>
     <row r="11" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B11" s="16" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>35</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="E11" s="16">
+        <v>16</v>
+      </c>
+      <c r="J11" s="31"/>
     </row>
     <row r="12" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>35</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="E12" s="16">
+        <v>10</v>
+      </c>
+      <c r="J12" s="31"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <f>SUM(E7:E12)</f>
+        <v>137</v>
+      </c>
+      <c r="J13" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1553,7 +1540,8 @@
   <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="8" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
     <col min="3" max="3" width="38" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
@@ -1566,785 +1554,785 @@
   <sheetData>
     <row r="1" spans="1:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="17" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="9" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="H9" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="I9" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="J9" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="F9" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>72</v>
-      </c>
       <c r="K9" s="14" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="103.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F10" s="20">
         <v>3</v>
       </c>
       <c r="G10" s="20" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H10" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I10" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J10" s="20" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K10" s="20" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F11" s="20">
         <v>5</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J11" s="20" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="K11" s="20" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F12" s="20">
         <v>8</v>
       </c>
       <c r="G12" s="20" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="H12" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I12" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J12" s="20" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="K12" s="20" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="B13" s="20" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F13" s="20">
         <v>3</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J13" s="20" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K13" s="20" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F14" s="20">
         <v>3</v>
       </c>
       <c r="G14" s="20" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H14" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I14" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J14" s="20" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="K14" s="20" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F15" s="20">
         <v>3</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J15" s="20" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="K15" s="20" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F16" s="20">
         <v>3</v>
       </c>
       <c r="G16" s="20" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="H16" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J16" s="20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="19" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F17" s="20">
         <v>5</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J17" s="20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K17" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E18" s="22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F18" s="20">
         <v>5</v>
       </c>
       <c r="G18" s="20" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="H18" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I18" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J18" s="20" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K18" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E19" s="22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F19" s="20">
         <v>3</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="H19" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I19" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J19" s="20" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E20" s="22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F20" s="20">
         <v>5</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I20" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J20" s="20" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F21" s="20">
         <v>5</v>
       </c>
       <c r="G21" s="20" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="H21" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I21" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J21" s="20" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F22" s="20">
         <v>5</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J22" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F23" s="20">
         <v>8</v>
       </c>
       <c r="G23" s="20" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="H23" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I23" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J23" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F24" s="20">
         <v>13</v>
       </c>
       <c r="G24" s="20" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="H24" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I24" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J24" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K24" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="19" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C25" s="20" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F25" s="20">
         <v>8</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I25" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J25" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K25" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="19" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D26" s="20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E26" s="23" t="s">
         <v>120</v>
-      </c>
-      <c r="E26" s="23" t="s">
-        <v>125</v>
       </c>
       <c r="F26" s="20">
         <v>5</v>
       </c>
       <c r="G26" s="20" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="H26" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="I26" s="20" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="J26" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K26" s="20" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="19" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F27" s="20">
         <v>13</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I27" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J27" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K27" s="20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F28" s="20">
         <v>21</v>
       </c>
       <c r="G28" s="20" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="H28" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I28" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J28" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K28" s="20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B29" s="20" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C29" s="20" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D29" s="20" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E29" s="24" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F29" s="20">
         <v>13</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="I29" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J29" s="20" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K29" s="20" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="B30" s="26"/>
       <c r="C30" s="26"/>
@@ -2354,7 +2342,7 @@
         <v>137</v>
       </c>
       <c r="G30" s="27" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H30" s="26"/>
       <c r="I30" s="26"/>
@@ -2376,117 +2364,117 @@
   <sheetData>
     <row r="1" spans="1:1" ht="23.25" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A4" s="28" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="29" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="29" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="29" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="29" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="29" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="29" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A17" s="28" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="29" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="29" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="29" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="29" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="29" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="29" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="29" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="29" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="29" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2507,113 +2495,113 @@
   <sheetData>
     <row r="2" spans="1:4" ht="18.75" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B3" s="9" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="14"/>
       <c r="B5" s="14" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D5" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="30" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C6" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D6" s="30"/>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="30" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D7" s="30"/>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="30" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D8" s="30"/>
     </row>
     <row r="9" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="30" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C9" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D9" s="30"/>
     </row>
     <row r="10" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="30" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D10" s="30"/>
     </row>
     <row r="11" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="30" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="C11" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D11" s="30"/>
     </row>
     <row r="12" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="30" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C12" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D12" s="30"/>
     </row>
     <row r="13" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="30" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C13" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D13" s="30"/>
     </row>
     <row r="14" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="30" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C14" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D14" s="30"/>
     </row>
     <row r="15" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="30" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C15" s="31" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D15" s="30"/>
     </row>
